--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_176_R18.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_176_R18.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0599</v>
+        <v>2.7449</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1159</v>
+        <v>3.6934</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.056</v>
+        <v>-0.9485</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4841</v>
+        <v>0.7866</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7091</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.225</v>
+        <v>1.4756</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1935</v>
+        <v>3.3458</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2069</v>
+        <v>-0.077</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0134</v>
+        <v>3.4229</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.7094</v>
+        <v>-2.5592</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4978</v>
+        <v>-0.612</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.2116</v>
+        <v>-1.9473</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3645</v>
+        <v>0.2625</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7986</v>
+        <v>-0.1885</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5658</v>
+        <v>0.4509</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2836</v>
+        <v>0.5361</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2836</v>
+        <v>0.5361</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9397</v>
+        <v>2.1477</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8547</v>
+        <v>2.2037</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9149</v>
+        <v>-0.056</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7866</v>
+        <v>0.4841</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6889999999999999</v>
+        <v>2.7091</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4756</v>
+        <v>-2.225</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3458</v>
+        <v>3.1935</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.077</v>
+        <v>3.2069</v>
       </c>
       <c r="L3" t="n">
-        <v>3.4229</v>
+        <v>-0.0134</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5592</v>
+        <v>-2.7094</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.612</v>
+        <v>-0.4978</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9473</v>
+        <v>-2.2116</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4573</v>
+        <v>0.4523</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0272</v>
+        <v>-0.1136</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4846</v>
+        <v>0.5658</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5361</v>
+        <v>0.2836</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5361</v>
+        <v>0.2836</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.704</v>
+        <v>0.7775</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4736</v>
+        <v>1.6479</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7696</v>
+        <v>-0.8704</v>
       </c>
       <c r="G4" t="n">
         <v>0.7476</v>
@@ -766,13 +766,13 @@
         <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6548</v>
+        <v>0.7284</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3566</v>
+        <v>0.5309</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2983</v>
+        <v>0.1975</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9304</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0553</v>
+        <v>0.3317</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5293</v>
+        <v>0.518</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5846</v>
+        <v>-0.1863</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4529</v>
+        <v>-0.3454</v>
       </c>
       <c r="H5" t="n">
-        <v>0.287</v>
+        <v>1.5819</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.7399</v>
+        <v>-1.9273</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5486</v>
+        <v>2.4462</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7093</v>
+        <v>2.2154</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1607</v>
+        <v>0.2308</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0016</v>
+        <v>-2.7916</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4223</v>
+        <v>-0.6335</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5792</v>
+        <v>-2.1581</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3917</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2199</v>
+        <v>-0.0756</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0193</v>
+        <v>-0.5933</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2393</v>
+        <v>0.5177</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.214</v>
+        <v>2.1444</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6694</v>
+        <v>0.0036</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3823</v>
+        <v>0.9578</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2871</v>
+        <v>-0.9542</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3454</v>
+        <v>-1.4529</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5819</v>
+        <v>0.287</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.9273</v>
+        <v>-1.7399</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4462</v>
+        <v>0.5486</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2154</v>
+        <v>0.7093</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2308</v>
+        <v>-0.1607</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7916</v>
+        <v>-2.0016</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6335</v>
+        <v>-0.4223</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1581</v>
+        <v>-1.5792</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3917</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0767</v>
+        <v>1.2788</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.4936</v>
+        <v>0.4092</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4169</v>
+        <v>0.8696</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1444</v>
+        <v>-1.214</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2659</v>
+        <v>-0.7365</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5905</v>
+        <v>1.0191</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8564</v>
+        <v>-1.7556</v>
       </c>
       <c r="G7" t="n">
         <v>0.1872</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6128</v>
+        <v>-0.0835</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4402</v>
+        <v>-0.0116</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1726</v>
+        <v>-0.0718</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0722</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8397</v>
+        <v>-3.5454</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5849</v>
+        <v>-2.4815</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2548</v>
+        <v>-1.0639</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.9384</v>
+        <v>-3.2973</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.4165</v>
+        <v>1.4573</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5219</v>
+        <v>-4.7546</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7796</v>
+        <v>0.0838</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.9941</v>
+        <v>2.2588</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2146</v>
+        <v>-2.175</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1588</v>
+        <v>-3.3812</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4223</v>
+        <v>-0.8016</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7365</v>
+        <v>-2.5796</v>
       </c>
       <c r="P8" t="n">
         <v>-0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6528</v>
+        <v>-0.5522</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6765</v>
+        <v>-0.782</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0237</v>
+        <v>0.2298</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.5361</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.5361</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3028</v>
+        <v>-3.6795</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.3843</v>
+        <v>-4.7946</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0815</v>
+        <v>1.1151</v>
       </c>
       <c r="G9" t="n">
         <v>-5.1859</v>
@@ -1156,13 +1156,13 @@
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5988</v>
+        <v>0.0246</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0455</v>
+        <v>-0.4558</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4468</v>
+        <v>0.4804</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3682</v>
+        <v>-3.7086</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1027</v>
+        <v>-2.4539</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2655</v>
+        <v>-1.2548</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2973</v>
+        <v>-3.9384</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4573</v>
+        <v>-3.4165</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.7546</v>
+        <v>-0.5219</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0838</v>
+        <v>-1.7796</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2588</v>
+        <v>-2.9941</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.175</v>
+        <v>1.2146</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.3812</v>
+        <v>-2.1588</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8016</v>
+        <v>-0.4223</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.5796</v>
+        <v>-1.7365</v>
       </c>
       <c r="P10" t="n">
         <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.375</v>
+        <v>-0.2161</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4031</v>
+        <v>-0.1924</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0281</v>
+        <v>-0.0237</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5361</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5361</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4633</v>
+        <v>-3.8496</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2368</v>
+        <v>-2.6903</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2265</v>
+        <v>-1.1593</v>
       </c>
       <c r="G11" t="n">
         <v>-3.5294</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4577</v>
+        <v>1.0714</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1687</v>
+        <v>0.3778</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6264</v>
+        <v>0.6937</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,31 +1345,31 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.261</v>
+        <v>-9.514200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.127000000000001</v>
+        <v>-2.380400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.1339</v>
+        <v>-7.133899999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-15.5438</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2155999999999996</v>
+        <v>0.2155999999999991</v>
       </c>
       <c r="I12" t="n">
         <v>-15.7595</v>
       </c>
       <c r="J12" t="n">
-        <v>5.687200000000001</v>
+        <v>5.687199999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6007</v>
+        <v>4.600700000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0867</v>
+        <v>1.086699999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-21.2314</v>
@@ -1390,13 +1390,13 @@
         <v>12.7576</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1437</v>
+        <v>2.8906</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7659</v>
+        <v>-1.0193</v>
       </c>
       <c r="U12" t="n">
-        <v>3.909899999999999</v>
+        <v>3.9099</v>
       </c>
       <c r="V12" t="n">
         <v>0.8196999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.6254</v>
+        <v>7.6299</v>
       </c>
       <c r="E13" t="n">
-        <v>7.2742</v>
+        <v>7.6281</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6488</v>
+        <v>0.0018</v>
       </c>
       <c r="G13" t="n">
         <v>7.8039</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.498</v>
+        <v>-0.4935</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.187</v>
+        <v>-0.8331</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.311</v>
+        <v>0.3396</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3416</v>
+        <v>3.3201</v>
       </c>
       <c r="E14" t="n">
         <v>1.8764</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4652</v>
+        <v>1.4437</v>
       </c>
       <c r="G14" t="n">
         <v>2.8399</v>
@@ -1546,13 +1546,13 @@
         <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0351</v>
+        <v>0.0136</v>
       </c>
       <c r="T14" t="n">
         <v>-0.5228</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5579</v>
+        <v>0.5364</v>
       </c>
       <c r="V14" t="n">
         <v>0.9304</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. KALAITZAKIS</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2806</v>
+        <v>2.0406</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8993</v>
+        <v>1.4808</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3813</v>
+        <v>0.5598</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0799</v>
+        <v>2.8142</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4274</v>
+        <v>0.5089</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6524</v>
+        <v>2.3053</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1981</v>
+        <v>3.6438</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8066</v>
+        <v>0.703</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3914</v>
+        <v>2.9409</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1182</v>
+        <v>-0.8297</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3792</v>
+        <v>-0.1941</v>
       </c>
       <c r="O15" t="n">
-        <v>0.261</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2631</v>
+        <v>0.1542</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2987</v>
+        <v>-0.6838</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0356</v>
+        <v>0.838</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>P. KALAITZAKIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9353</v>
+        <v>1.1633</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1269</v>
+        <v>1.0173</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1917</v>
+        <v>0.146</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8142</v>
+        <v>1.0799</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5089</v>
+        <v>0.4274</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3053</v>
+        <v>0.6524</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6438</v>
+        <v>1.1981</v>
       </c>
       <c r="K16" t="n">
-        <v>0.703</v>
+        <v>0.8066</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9409</v>
+        <v>0.3914</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8297</v>
+        <v>-0.1182</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1941</v>
+        <v>-0.3792</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.261</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-0.3804</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0376</v>
+        <v>-0.1808</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0866</v>
+        <v>-0.1997</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7018</v>
+        <v>1.0863</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7285</v>
+        <v>0.6535</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4304</v>
+        <v>0.4328</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3715</v>
+        <v>3.2219</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8428</v>
+        <v>-0.7229</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5286999999999999</v>
+        <v>3.9448</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1859</v>
+        <v>4.384</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0755</v>
+        <v>0.0679</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1104</v>
+        <v>4.3161</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1856</v>
+        <v>-1.1621</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2327</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4183</v>
+        <v>-0.3713</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6959</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>-3.4793</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3681</v>
+        <v>0.2741</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5228</v>
+        <v>-0.393</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1546</v>
+        <v>0.6671</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3943</v>
+        <v>0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4972</v>
+        <v>0.6626</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2997</v>
+        <v>-0.7212</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1975</v>
+        <v>1.3838</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2219</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7229</v>
+        <v>-1.2591</v>
       </c>
       <c r="I18" t="n">
-        <v>3.9448</v>
+        <v>2.1548</v>
       </c>
       <c r="J18" t="n">
-        <v>4.384</v>
+        <v>1.5469</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0679</v>
+        <v>-0.5609</v>
       </c>
       <c r="L18" t="n">
-        <v>4.3161</v>
+        <v>2.1078</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1621</v>
+        <v>-0.6512</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.6982</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3713</v>
+        <v>0.047</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4793</v>
+        <v>-1.3917</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.315</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7468</v>
+        <v>-0.8764</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4318</v>
+        <v>-0.0525</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4541</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8996</v>
+        <v>-0.6106</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3537</v>
+        <v>1.1615</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7945</v>
+        <v>1.3715</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8485</v>
+        <v>0.8428</v>
       </c>
       <c r="I19" t="n">
-        <v>1.054</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5581</v>
+        <v>1.1859</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4046</v>
+        <v>1.0755</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8465</v>
+        <v>0.1104</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2364</v>
+        <v>0.1856</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4439</v>
+        <v>-0.2327</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2075</v>
+        <v>0.4183</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.6959</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-1.3917</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7821</v>
+        <v>-0.519</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8363</v>
+        <v>-0.4048</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9458</v>
+        <v>-0.1142</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1418</v>
+        <v>0.3943</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2836</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0326</v>
+        <v>-0.3428</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3578</v>
+        <v>-0.7116</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3904</v>
+        <v>0.3689</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3195</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8883</v>
+        <v>0.5129</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2715</v>
+        <v>-0.0824</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6168</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>N. ROGKAVOPOULOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3919</v>
+        <v>-0.362</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9571</v>
+        <v>0.0147</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5652</v>
+        <v>-0.3768</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8957000000000001</v>
+        <v>-0.2692</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2591</v>
+        <v>-0.4632</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1548</v>
+        <v>0.1941</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5469</v>
+        <v>0.1208</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5609</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>2.1078</v>
+        <v>0.0368</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6512</v>
+        <v>-0.39</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6982</v>
+        <v>-0.5473</v>
       </c>
       <c r="O21" t="n">
-        <v>0.047</v>
+        <v>0.1573</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9834</v>
+        <v>-0.0206</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1123</v>
+        <v>-0.1061</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8711</v>
+        <v>0.0854</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. ROGKAVOPOULOS</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5808</v>
+        <v>-1.5999</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1032</v>
+        <v>-2.315</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4776</v>
+        <v>0.7151</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2692</v>
+        <v>-0.7945</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4632</v>
+        <v>-1.8485</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1941</v>
+        <v>1.054</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1208</v>
+        <v>-0.5581</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08400000000000001</v>
+        <v>-1.4046</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0368</v>
+        <v>0.8465</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.39</v>
+        <v>-0.2364</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5473</v>
+        <v>-0.4439</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1573</v>
+        <v>0.2075</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2394</v>
+        <v>0.7281</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.224</v>
+        <v>0.4208</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0154</v>
+        <v>0.3073</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5361</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.635</v>
+        <v>-2.3154</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2964</v>
+        <v>-1.1785</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3386</v>
+        <v>-1.1369</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0997</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2311</v>
+        <v>0.0885</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3655</v>
+        <v>-0.2475</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1344</v>
+        <v>0.3361</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10.2609</v>
+        <v>11.8336</v>
       </c>
       <c r="E24" t="n">
         <v>7.133900000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>3.127</v>
+        <v>4.6997</v>
       </c>
       <c r="G24" t="n">
         <v>15.5441</v>
@@ -2317,7 +2317,7 @@
         <v>-1.0865</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.319500000000001</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q24" t="n">
         <v>-12.7574</v>
@@ -2326,13 +2326,13 @@
         <v>10.438</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.1437</v>
+        <v>-0.571</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.9097</v>
+        <v>-3.9099</v>
       </c>
       <c r="U24" t="n">
-        <v>1.766</v>
+        <v>3.3388</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8197000000000001</v>
